--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260622.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260622.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>13.70%</t>
+          <t>14.62%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.90%</t>
+          <t>9.77%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>6.18%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>5.85%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.57%</t>
+          <t>5.44%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.64%</t>
+          <t>4.52%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.15%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -814,90 +814,90 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2,793,000</t>
+          <t>19,329,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>19,329,000</t>
+          <t>2,793,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>15,094,000</t>
+          <t>14,170,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>14,170,000</t>
+          <t>15,094,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -946,24 +946,24 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>14,694,000</t>
+          <t>1,088,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,22 +975,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台灣積體</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,088,000</t>
+          <t>14,694,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>宏碁股份</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>61,597,000</t>
+          <t>2,180,703,214</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,369 +1085,369 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>宏碁股份</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>4,506,000</t>
+          <t>61,597,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>和碩聯合</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>23,330,000</t>
+          <t>4,506,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>頎邦科技</t>
+          <t>和碩聯合</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>6,921,000</t>
+          <t>23,330,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>頎邦科技</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>18,083,000</t>
+          <t>6,921,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>7,540,000</t>
+          <t>18,083,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>202607WTX</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>115/07台股期貨</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>7,540,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>202607WTX</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>家登精密</t>
+          <t>115/07台股期貨</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,664,000</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>家登精密</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,930,000</t>
+          <t>2,664,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,846,000</t>
+          <t>1,930,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,278,000</t>
+          <t>1,846,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>970,598,378</t>
+          <t>14,278,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>29,406,000</t>
+          <t>1,024,230,378</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>群光電子</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>6,681,000</t>
+          <t>29,406,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>群光電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,755,000</t>
+          <t>6,681,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>4,075,000</t>
+          <t>1,755,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,412,000</t>
+          <t>4,075,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>678,158,420</t>
+          <t>3,412,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-323,938,551</t>
+          <t>-372,044,019</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.25%</t>
         </is>
       </c>
     </row>
